--- a/plantillas_117_integradas_v7/Plantilla_Excel_Bloque_61_IN_Piura.xlsx
+++ b/plantillas_117_integradas_v7/Plantilla_Excel_Bloque_61_IN_Piura.xlsx
@@ -574,7 +574,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B29</f>
+              <f>'Gráficos de integración'!B27</f>
             </strRef>
           </tx>
           <spPr>
@@ -584,12 +584,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$30:$A$34</f>
+              <f>'Gráficos de integración'!$A$28:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$30:$B$34</f>
+              <f>'Gráficos de integración'!$B$28:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -669,7 +669,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B52</f>
+              <f>'Gráficos de integración'!B46</f>
             </strRef>
           </tx>
           <spPr>
@@ -679,12 +679,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$53:$A$57</f>
+              <f>'Gráficos de integración'!$A$47:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$53:$B$57</f>
+              <f>'Gráficos de integración'!$B$47:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -764,7 +764,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B75</f>
+              <f>'Gráficos de integración'!B65</f>
             </strRef>
           </tx>
           <spPr>
@@ -774,12 +774,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$76:$A$78</f>
+              <f>'Gráficos de integración'!$A$66:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$76:$B$78</f>
+              <f>'Gráficos de integración'!$B$66:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -857,7 +857,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Gráficos de integración'!B96</f>
+              <f>'Gráficos de integración'!B84</f>
             </strRef>
           </tx>
           <spPr>
@@ -867,12 +867,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficos de integración'!$A$97:$A$100</f>
+              <f>'Gráficos de integración'!$A$85:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficos de integración'!$B$97:$B$100</f>
+              <f>'Gráficos de integración'!$B$85:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -916,7 +916,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -938,7 +938,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -960,7 +960,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
@@ -982,7 +982,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -3422,7 +3422,7 @@
     <row r="6">
       <c r="A6" s="51" t="inlineStr">
         <is>
-          <t>Cruce de la ficha de campo F-DT vigente con la ficha de resumen de gabinete y el catálogo maestro. Integración 2026-09-11 20:22:30.</t>
+          <t>Cruce de la ficha de campo F-DT vigente con la ficha de resumen de gabinete y el catálogo maestro. Integración 2026-09-11 21:26:28.</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -7437,249 +7437,249 @@
         <v>14</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>Estado del cruce entre fuentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>Estado del cruce entre fuentes</t>
-        </is>
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="54" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="B29" s="54" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>COMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="B29" s="56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="55" t="inlineStr">
         <is>
-          <t>CONFORME</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="B30" s="55" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="56" t="inlineStr">
         <is>
-          <t>COMPLEMENTADO</t>
+          <t>DISCREPANTE</t>
         </is>
       </c>
       <c r="B31" s="56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="55" t="inlineStr">
         <is>
-          <t>ACTUALIZADO</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="B32" s="55" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="56" t="inlineStr">
-        <is>
-          <t>DISCREPANTE</t>
-        </is>
-      </c>
-      <c r="B33" s="56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="B34" s="55" t="n">
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
+        <is>
+          <t>Cobertura por estrato — campo (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>Estrato</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="inlineStr">
+        <is>
+          <t>% del área</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="55" t="inlineStr">
+        <is>
+          <t>Dosel</t>
+        </is>
+      </c>
+      <c r="B47" s="60" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>Arbustiva</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="n">
         <v>10</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="55" t="inlineStr">
+        <is>
+          <t>Herbácea</t>
+        </is>
+      </c>
+      <c r="B49" s="60" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>Hojarasca</t>
+        </is>
+      </c>
+      <c r="B50" s="62" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
-        <is>
-          <t>Cobertura por estrato — campo (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="54" t="inlineStr">
-        <is>
-          <t>Estrato</t>
-        </is>
-      </c>
-      <c r="B52" s="54" t="inlineStr">
-        <is>
-          <t>% del área</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="55" t="inlineStr">
-        <is>
-          <t>Dosel</t>
-        </is>
-      </c>
-      <c r="B53" s="60" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="56" t="inlineStr">
-        <is>
-          <t>Arbustiva</t>
-        </is>
-      </c>
-      <c r="B54" s="61" t="n">
+      <c r="A51" s="55" t="inlineStr">
+        <is>
+          <t>Suelo desnudo</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="53" t="inlineStr">
+        <is>
+          <t>Causas activas de degradación (F-DT-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
+          <t>Causa</t>
+        </is>
+      </c>
+      <c r="B65" s="54" t="inlineStr">
+        <is>
+          <t>Intensidad (1 ligera - 4 muy fuerte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="55" t="inlineStr">
+        <is>
+          <t>Cambio de uso a agricultura</t>
+        </is>
+      </c>
+      <c r="B66" s="55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>Cambio de uso a pastoreo</t>
+        </is>
+      </c>
+      <c r="B67" s="56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="55" t="inlineStr">
+        <is>
+          <t>Sobrepastoreo (caprino/vacuno)</t>
+        </is>
+      </c>
+      <c r="B68" s="55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="53" t="inlineStr">
+        <is>
+          <t>Control de consistencia por calificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="54" t="inlineStr">
+        <is>
+          <t>Calificación</t>
+        </is>
+      </c>
+      <c r="B84" s="54" t="inlineStr">
+        <is>
+          <t>Verificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="55" t="inlineStr">
+        <is>
+          <t>SUSTANTIVA</t>
+        </is>
+      </c>
+      <c r="B85" s="55" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="56" t="inlineStr">
+        <is>
+          <t>NO SUSTANTIVA</t>
+        </is>
+      </c>
+      <c r="B86" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="55" t="inlineStr">
+        <is>
+          <t>CORREGIDO</t>
+        </is>
+      </c>
+      <c r="B87" s="55" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="55" t="inlineStr">
-        <is>
-          <t>Herbácea</t>
-        </is>
-      </c>
-      <c r="B55" s="60" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="56" t="inlineStr">
-        <is>
-          <t>Hojarasca</t>
-        </is>
-      </c>
-      <c r="B56" s="62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="55" t="inlineStr">
-        <is>
-          <t>Suelo desnudo</t>
-        </is>
-      </c>
-      <c r="B57" s="63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="53" t="inlineStr">
-        <is>
-          <t>Causas activas de degradación (F-DT-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="54" t="inlineStr">
-        <is>
-          <t>Causa</t>
-        </is>
-      </c>
-      <c r="B75" s="54" t="inlineStr">
-        <is>
-          <t>Intensidad (1 ligera - 4 muy fuerte)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="55" t="inlineStr">
-        <is>
-          <t>Cambio de uso a agricultura</t>
-        </is>
-      </c>
-      <c r="B76" s="55" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="56" t="inlineStr">
-        <is>
-          <t>Cambio de uso a pastoreo</t>
-        </is>
-      </c>
-      <c r="B77" s="56" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="55" t="inlineStr">
-        <is>
-          <t>Sobrepastoreo (caprino/vacuno)</t>
-        </is>
-      </c>
-      <c r="B78" s="55" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="53" t="inlineStr">
-        <is>
-          <t>Control de consistencia por calificación</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="54" t="inlineStr">
-        <is>
-          <t>Calificación</t>
-        </is>
-      </c>
-      <c r="B96" s="54" t="inlineStr">
-        <is>
-          <t>Verificaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="55" t="inlineStr">
-        <is>
-          <t>SUSTANTIVA</t>
-        </is>
-      </c>
-      <c r="B97" s="55" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="56" t="inlineStr">
-        <is>
-          <t>NO SUSTANTIVA</t>
-        </is>
-      </c>
-      <c r="B98" s="56" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="55" t="inlineStr">
-        <is>
-          <t>CORREGIDO</t>
-        </is>
-      </c>
-      <c r="B99" s="55" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="56" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="56" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="B100" s="56" t="n">
+      <c r="B88" s="56" t="n">
         <v>11</v>
       </c>
     </row>
